--- a/examples/output/phase1-dotnet-poi-write.xlsx
+++ b/examples/output/phase1-dotnet-poi-write.xlsx
@@ -2,6 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr date1904="false"/>
+  <bookViews>
+    <workbookView activeTab="0"/>
+  </bookViews>
   <sheets>
     <sheet name="Dotnet" r:id="rId3" sheetId="1"/>
   </sheets>
